--- a/ig/DM-JANVIER-2026/ASS-X08-TranscoSavoirFaireR01-SavoirFaire.xlsx
+++ b/ig/DM-JANVIER-2026/ASS-X08-TranscoSavoirFaireR01-SavoirFaire.xlsx
@@ -105,7 +105,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R01-EnsembleSavoirFaire-CISIS/FHIR/TRE-R01-EnsembleSavoirFaire-CISIS|20241213120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R01-EnsembleSavoirFaire-CISIS/FHIR/TRE-R01-EnsembleSavoirFaire-CISIS|20260202120000</t>
   </si>
   <si>
     <t/>
